--- a/outputs/ZR751/parameters/MK-2206_parameters.xlsx
+++ b/outputs/ZR751/parameters/MK-2206_parameters.xlsx
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2017057472541689</v>
+        <v>0.20172065427312</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9409798523102033</v>
+        <v>0.9409690579854687</v>
       </c>
     </row>
     <row r="4">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1985344776524128</v>
+        <v>0.1985295900294139</v>
       </c>
     </row>
     <row r="5">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4689728984482955</v>
+        <v>0.468995697226619</v>
       </c>
     </row>
   </sheetData>
